--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N30_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>5.427872999691954</v>
+        <v>0.8820293624499426</v>
       </c>
       <c r="D2" t="n">
-        <v>5.370961558923272</v>
+        <v>0.8727812533250316</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
